--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831370</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831758</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1294,6 +1319,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831759</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1419,6 +1449,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831766</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1549,6 +1584,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831373</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1674,6 +1714,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831610</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1799,6 +1844,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831613</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1929,6 +1979,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831622</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2054,6 +2109,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831628</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2179,6 +2239,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831769</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2304,6 +2369,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831778</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2429,6 +2499,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831780</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2559,6 +2634,11 @@
           <t>C250098 - Vällersten häckfågelinventering 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831385</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2661,6 +2741,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092261</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2763,6 +2848,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092262</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2860,6 +2950,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092245</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2962,6 +3057,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092200</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3075,6 +3175,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67743648</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3176,6 +3281,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67743635</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3287,8 +3397,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87462034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67743635</v>
+        <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>97987</v>
+        <v>98063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3194,36 +3194,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>224364</v>
+        <v>221946</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vällersten, Sm</t>
+          <t>Källäng, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443009</v>
+        <v>443022</v>
       </c>
       <c r="R22" t="n">
-        <v>6344492</v>
+        <v>6344501</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3247,12 +3248,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3263,83 +3274,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lennart Persson, Margareta Edqvist</t>
+          <t>Tommy Carlström, Ingela Carlström, Isac Dahlström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67743635</t>
+          <t>https://artportalen.se/Sighting/135590278</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>87462034</v>
+        <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>107908</v>
+        <v>99504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219955</v>
+        <v>222857</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hörle Källäng 540 m O-OSO, Sm</t>
+          <t>Källäng, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443007</v>
+        <v>443022</v>
       </c>
       <c r="R23" t="n">
-        <v>6344476</v>
+        <v>6344501</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3363,12 +3360,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3379,25 +3386,242 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Skogsstig i tallmo</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lennart Persson, Johan Hjerpe</t>
+          <t>Tommy Carlström, Ingela Carlström, Isac Dahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135590312</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>67743635</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vällersten, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>443009</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6344492</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lennart Persson, Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67743635</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>87462034</v>
+      </c>
+      <c r="B25" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hörle Källäng 540 m O-OSO, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>443007</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6344476</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-08-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-08-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Skogsstig i tallmo</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lennart Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lennart Persson, Johan Hjerpe</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/87462034</t>
         </is>
@@ -3427,6 +3651,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -3186,7 +3186,7 @@
         <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>99504</v>
+        <v>99551</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -3186,7 +3186,7 @@
         <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>99551</v>
+        <v>99578</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67743635</v>
+        <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>97987</v>
+        <v>98139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3194,36 +3194,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>224364</v>
+        <v>221946</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vällersten, Sm</t>
+          <t>Källäng, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443009</v>
+        <v>443022</v>
       </c>
       <c r="R22" t="n">
-        <v>6344492</v>
+        <v>6344501</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3247,12 +3248,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3263,83 +3274,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lennart Persson, Margareta Edqvist</t>
+          <t>Tommy Carlström, Ingela Carlström, Isac Dahlström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67743635</t>
+          <t>https://artportalen.se/Sighting/135590278</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>87462034</v>
+        <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>107908</v>
+        <v>99583</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219955</v>
+        <v>222857</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hörle Källäng 540 m O-OSO, Sm</t>
+          <t>Källäng, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443007</v>
+        <v>443022</v>
       </c>
       <c r="R23" t="n">
-        <v>6344476</v>
+        <v>6344501</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3363,12 +3360,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3379,25 +3386,242 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Skogsstig i tallmo</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lennart Persson, Johan Hjerpe</t>
+          <t>Tommy Carlström, Ingela Carlström, Isac Dahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135590312</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>67743635</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vällersten, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>443009</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6344492</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lennart Persson, Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67743635</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>87462034</v>
+      </c>
+      <c r="B25" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hörle Källäng 540 m O-OSO, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>443007</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6344476</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-08-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-08-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Skogsstig i tallmo</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lennart Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lennart Persson, Johan Hjerpe</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/87462034</t>
         </is>
@@ -3427,6 +3651,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -3186,7 +3186,7 @@
         <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>99583</v>
+        <v>99585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -3186,7 +3186,7 @@
         <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>98141</v>
+        <v>98158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>99585</v>
+        <v>99602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -3186,7 +3186,7 @@
         <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>99602</v>
+        <v>99603</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 1453-2026 artfynd.xlsx
+++ b/artfynd/S 1453-2026 artfynd.xlsx
@@ -3186,7 +3186,7 @@
         <v>135590278</v>
       </c>
       <c r="B22" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>135590312</v>
       </c>
       <c r="B23" t="n">
-        <v>99603</v>
+        <v>99604</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
